--- a/02_DIA_inicio_2026_analisis_assets/rbd_9611_escuela-basica-tupahue_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9611_escuela-basica-tupahue_nt2_rubricas.xlsx
@@ -1800,13 +1800,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1D9411F-7883-4AC2-98F6-456399BB8C44}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAF70649-BACC-4164-B95C-E01EB88520D3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7C35CA7-79CC-443B-BF8B-B267849BC67E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38B92871-5F0E-4CC2-9F65-C18545A5D224}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D198721-0FB5-4A19-9476-154396A13B2E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90313D10-D124-4DAD-94D6-E1FB4281C921}"/>
 </file>